--- a/data/trans_dic/P5_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P5_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con algún problema medioambiental importante en la zona de residencia</t>
+          <t>Hogares con algún problema medioambiental importante en la zona de residencia (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,07; 36,89</t>
+          <t>19,69; 35,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,04; 47,68</t>
+          <t>27,95; 48,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,97; 49,77</t>
+          <t>31,09; 49,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,13; 26,5</t>
+          <t>13,34; 26,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,83; 35,79</t>
+          <t>19,13; 34,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,71; 53,17</t>
+          <t>33,52; 52,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,89; 48,21</t>
+          <t>30,45; 48,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,28; 24,41</t>
+          <t>12,27; 24,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,49; 33,01</t>
+          <t>21,77; 33,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34,28; 47,94</t>
+          <t>33,77; 47,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,69; 46,7</t>
+          <t>32,84; 46,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,45; 23,45</t>
+          <t>14,42; 23,44</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,85; 25,92</t>
+          <t>11,41; 26,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,71; 46,7</t>
+          <t>27,27; 47,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,86; 44,36</t>
+          <t>27,03; 44,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,4; 25,29</t>
+          <t>11,59; 25,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,95; 28,52</t>
+          <t>13,47; 29,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,82; 55,4</t>
+          <t>35,62; 54,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,37; 41,94</t>
+          <t>26,16; 41,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,47; 24,25</t>
+          <t>9,62; 24,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,31; 24,72</t>
+          <t>14,4; 24,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,98; 48,13</t>
+          <t>34,23; 48,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,05; 40,44</t>
+          <t>28,53; 40,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,32; 23,07</t>
+          <t>13,07; 22,29</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,25; 29,44</t>
+          <t>12,36; 29,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,86; 41,1</t>
+          <t>22,05; 41,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,56; 44,86</t>
+          <t>22,95; 46,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,23; 30,85</t>
+          <t>12,04; 31,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,76; 38,28</t>
+          <t>22,32; 38,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,73; 45,12</t>
+          <t>25,12; 44,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,41; 44,97</t>
+          <t>25,47; 44,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,66; 20,2</t>
+          <t>5,8; 20,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,43; 32,23</t>
+          <t>20,1; 32,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,74; 40,17</t>
+          <t>26,56; 39,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27,56; 41,83</t>
+          <t>27,08; 40,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,23; 21,27</t>
+          <t>10,16; 21,91</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,6; 38,64</t>
+          <t>26,52; 39,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,5; 51,5</t>
+          <t>37,52; 51,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,21; 38,16</t>
+          <t>26,5; 38,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,56; 50,9</t>
+          <t>13,37; 48,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,08; 34,14</t>
+          <t>22,11; 33,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,87; 40,81</t>
+          <t>28,32; 40,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,91; 44,09</t>
+          <t>32,79; 44,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,7; 24,97</t>
+          <t>14,32; 24,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,32; 34,33</t>
+          <t>25,35; 34,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34,6; 43,93</t>
+          <t>34,6; 43,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31,27; 39,9</t>
+          <t>30,95; 39,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,66; 40,08</t>
+          <t>15,98; 41,56</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,18; 41,66</t>
+          <t>23,63; 41,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,94; 39,39</t>
+          <t>22,59; 39,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,6; 41,1</t>
+          <t>25,86; 40,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,46; 31,82</t>
+          <t>18,48; 31,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,3; 42,14</t>
+          <t>25,83; 41,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,05; 43,14</t>
+          <t>27,23; 45,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,0; 47,05</t>
+          <t>30,96; 47,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,63; 22,8</t>
+          <t>11,52; 22,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,48; 39,49</t>
+          <t>27,35; 39,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27,5; 38,73</t>
+          <t>26,96; 38,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31,07; 42,12</t>
+          <t>30,35; 42,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,25; 24,52</t>
+          <t>16,11; 24,45</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,3; 40,19</t>
+          <t>22,66; 40,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34,74; 58,14</t>
+          <t>35,18; 57,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,2; 49,85</t>
+          <t>29,64; 49,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,61; 20,57</t>
+          <t>6,52; 19,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,76; 36,82</t>
+          <t>19,81; 36,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,42; 53,61</t>
+          <t>35,08; 53,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,28; 49,57</t>
+          <t>29,88; 49,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,67; 26,86</t>
+          <t>11,56; 27,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,66; 36,03</t>
+          <t>23,93; 35,77</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37,96; 52,33</t>
+          <t>37,58; 51,91</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31,93; 46,09</t>
+          <t>32,58; 46,94</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,63; 21,86</t>
+          <t>10,69; 21,58</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25,0; 31,31</t>
+          <t>24,68; 31,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>34,46; 41,73</t>
+          <t>34,63; 41,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,59; 38,38</t>
+          <t>31,56; 38,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,11; 31,59</t>
+          <t>17,22; 34,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,8; 31,05</t>
+          <t>24,75; 30,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,7; 41,86</t>
+          <t>34,94; 41,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,87; 40,64</t>
+          <t>34,3; 40,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,8; 20,13</t>
+          <t>14,57; 19,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,63; 30,1</t>
+          <t>25,67; 30,27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35,82; 40,73</t>
+          <t>35,79; 40,68</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34,04; 38,97</t>
+          <t>33,64; 38,57</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,85; 25,43</t>
+          <t>16,79; 25,22</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con algún problema medioambiental importante en la zona de residencia (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>22371</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23050</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25846</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20163</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>18774</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>31813</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>30605</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>24052</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>41145</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>54864</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>56452</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>44216</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>15842; 28870</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17111; 29698</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20153; 32333</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13938; 27528</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>13706; 24990</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>24608; 38271</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>23829; 37869</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>16684; 33625</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>33111; 50618</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>45468; 64277</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>46988; 66111</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>34659; 56351</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>12343</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24076</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28965</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16904</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>13614</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>30933</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>31400</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>15769</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>25957</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>55009</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>60365</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>32673</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>7837; 18260</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>17829; 30821</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>22251; 36363</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>10969; 23765</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>9093; 19807</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>24411; 37301</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>24347; 38833</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>9193; 23211</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>19602; 33897</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>45835; 65115</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>50043; 71336</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>24866; 42405</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>11630</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20794</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16534</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10295</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>25332</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>23568</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>20918</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>36962</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>44362</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>37452</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>17398</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>7202; 16888</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14672; 27583</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11298; 22756</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6244; 16093</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>18740; 32034</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>17075; 29972</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>15537; 26994</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3703; 12913</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>28576; 45662</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>35724; 53427</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>29855; 44926</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>11757; 25355</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>48727</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>60391</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>53412</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>55323</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>40937</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>55188</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>65388</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>41089</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>89664</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>115578</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>118800</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>96412</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>40119; 59533</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>51214; 70204</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>43933; 63897</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>29068; 105071</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>32848; 49852</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>45702; 64942</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>56040; 75564</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>31256; 52713</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>76024; 102113</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>103061; 131021</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>104204; 133108</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>69640; 181059</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>22402</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28531</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>34163</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>29979</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>28762</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32247</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>38282</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>27339</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>51164</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>60778</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>72444</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>57318</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>16334; 28442</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>21109; 36795</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>26272; 41625</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>22072; 38117</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>21832; 35450</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>25058; 41409</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>30696; 46774</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>18733; 36789</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>42029; 61272</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>50000; 71647</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>60922; 84316</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>45444; 68972</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>23300</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>24566</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>23228</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8405</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>20229</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>32392</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>26801</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>13310</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>43528</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>56958</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>50028</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>21715</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>16964; 30576</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>18963; 31041</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>17539; 29347</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>4493; 13728</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>14337; 26127</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>25969; 39450</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>20263; 33566</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>8325; 20112</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>35237; 52672</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>48081; 66421</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>41368; 59603</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>15062; 30407</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>140772</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>181408</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>182148</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>141070</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>147647</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>206142</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>213394</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>128662</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>288419</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>387550</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>395542</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>269732</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>124058; 157946</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>165150; 199619</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>165047; 198858</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>113120; 223862</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>130804; 162956</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>187751; 224557</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>195603; 232052</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>108990; 148128</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>264699; 312169</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>363027; 412614</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>367665; 421624</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>235970; 354353</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P5_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P5_R-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,69; 35,88</t>
+          <t>20,25; 36,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,95; 48,51</t>
+          <t>27,89; 48,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,09; 49,87</t>
+          <t>30,33; 50,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,34; 26,35</t>
+          <t>13,67; 25,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,13; 34,88</t>
+          <t>18,87; 35,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,52; 52,13</t>
+          <t>33,28; 52,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,45; 48,39</t>
+          <t>29,95; 47,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,27; 24,73</t>
+          <t>11,98; 24,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,77; 33,28</t>
+          <t>21,35; 32,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33,77; 47,74</t>
+          <t>33,09; 47,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,84; 46,2</t>
+          <t>32,1; 45,82</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,42; 23,44</t>
+          <t>14,58; 23,22</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,41; 26,58</t>
+          <t>11,06; 26,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,27; 47,14</t>
+          <t>26,58; 46,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,03; 44,18</t>
+          <t>26,95; 43,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,59; 25,1</t>
+          <t>11,91; 25,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,47; 29,35</t>
+          <t>13,17; 29,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,62; 54,43</t>
+          <t>35,95; 55,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,16; 41,73</t>
+          <t>26,44; 42,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,62; 24,29</t>
+          <t>10,64; 23,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,4; 24,89</t>
+          <t>14,2; 25,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34,23; 48,63</t>
+          <t>33,9; 48,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,53; 40,68</t>
+          <t>29,15; 40,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,07; 22,29</t>
+          <t>13,26; 22,63</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,36; 29,0</t>
+          <t>12,33; 29,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,05; 41,46</t>
+          <t>23,01; 41,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,95; 46,23</t>
+          <t>23,77; 45,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,04; 31,03</t>
+          <t>11,39; 30,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,32; 38,16</t>
+          <t>22,44; 38,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,12; 44,1</t>
+          <t>25,56; 45,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,47; 44,24</t>
+          <t>25,39; 44,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,8; 20,22</t>
+          <t>5,6; 19,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,1; 32,11</t>
+          <t>20,88; 32,59</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,56; 39,73</t>
+          <t>26,51; 39,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27,08; 40,75</t>
+          <t>27,44; 41,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,16; 21,91</t>
+          <t>10,14; 21,47</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,52; 39,35</t>
+          <t>26,93; 38,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,52; 51,44</t>
+          <t>37,26; 51,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,5; 38,54</t>
+          <t>26,26; 38,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,37; 48,33</t>
+          <t>13,52; 52,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,11; 33,56</t>
+          <t>21,97; 33,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,32; 40,25</t>
+          <t>28,07; 40,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,79; 44,22</t>
+          <t>32,1; 44,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,32; 24,15</t>
+          <t>14,06; 23,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,35; 34,05</t>
+          <t>25,75; 33,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34,6; 43,99</t>
+          <t>34,61; 43,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,95; 39,54</t>
+          <t>31,14; 39,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,98; 41,56</t>
+          <t>15,56; 36,22</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23,63; 41,15</t>
+          <t>24,66; 43,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,59; 39,37</t>
+          <t>22,28; 38,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,86; 40,98</t>
+          <t>25,75; 41,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,48; 31,92</t>
+          <t>19,0; 32,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,83; 41,94</t>
+          <t>26,37; 42,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,23; 45,01</t>
+          <t>27,17; 43,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,96; 47,17</t>
+          <t>30,68; 45,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,52; 22,62</t>
+          <t>11,87; 22,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,35; 39,88</t>
+          <t>27,69; 39,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,96; 38,63</t>
+          <t>27,32; 38,45</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,35; 42,0</t>
+          <t>30,5; 42,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,11; 24,45</t>
+          <t>15,62; 25,02</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,66; 40,84</t>
+          <t>23,79; 40,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35,18; 57,58</t>
+          <t>34,7; 57,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,64; 49,6</t>
+          <t>28,63; 51,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,52; 19,93</t>
+          <t>6,81; 20,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,81; 36,09</t>
+          <t>20,12; 37,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,08; 53,28</t>
+          <t>34,14; 53,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,88; 49,49</t>
+          <t>29,55; 49,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,56; 27,93</t>
+          <t>11,86; 28,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,93; 35,77</t>
+          <t>23,72; 35,83</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37,58; 51,91</t>
+          <t>37,15; 51,87</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32,58; 46,94</t>
+          <t>31,79; 45,89</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,69; 21,58</t>
+          <t>10,4; 20,88</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>24,68; 31,42</t>
+          <t>24,79; 31,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>34,63; 41,85</t>
+          <t>34,52; 41,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,56; 38,03</t>
+          <t>31,46; 38,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,22; 34,09</t>
+          <t>17,28; 33,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,75; 30,83</t>
+          <t>25,14; 31,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,94; 41,79</t>
+          <t>34,85; 41,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,3; 40,7</t>
+          <t>33,84; 40,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,57; 19,8</t>
+          <t>14,68; 19,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,67; 30,27</t>
+          <t>25,82; 30,31</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35,79; 40,68</t>
+          <t>35,64; 40,9</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33,64; 38,57</t>
+          <t>33,81; 38,48</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,79; 25,22</t>
+          <t>16,82; 25,43</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15842; 28870</t>
+          <t>16291; 29078</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17111; 29698</t>
+          <t>17074; 29395</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20153; 32333</t>
+          <t>19661; 32679</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13938; 27528</t>
+          <t>14283; 26908</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13706; 24990</t>
+          <t>13520; 25274</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24608; 38271</t>
+          <t>24430; 38194</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23829; 37869</t>
+          <t>23435; 37444</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16684; 33625</t>
+          <t>16284; 32994</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33111; 50618</t>
+          <t>32470; 49795</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45468; 64277</t>
+          <t>44552; 64263</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46988; 66111</t>
+          <t>45928; 65567</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34659; 56351</t>
+          <t>35065; 55816</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7837; 18260</t>
+          <t>7594; 18454</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17829; 30821</t>
+          <t>17375; 30515</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22251; 36363</t>
+          <t>22183; 36161</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10969; 23765</t>
+          <t>11275; 23699</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9093; 19807</t>
+          <t>8888; 20117</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24411; 37301</t>
+          <t>24636; 37851</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24347; 38833</t>
+          <t>24608; 39152</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9193; 23211</t>
+          <t>10171; 22680</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19602; 33897</t>
+          <t>19341; 34087</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45835; 65115</t>
+          <t>45391; 65313</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50043; 71336</t>
+          <t>51114; 70599</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24866; 42405</t>
+          <t>25222; 43052</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7202; 16888</t>
+          <t>7182; 17342</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14672; 27583</t>
+          <t>15308; 27873</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11298; 22756</t>
+          <t>11700; 22235</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6244; 16093</t>
+          <t>5906; 15861</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18740; 32034</t>
+          <t>18837; 32581</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17075; 29972</t>
+          <t>17374; 30658</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15537; 26994</t>
+          <t>15489; 27284</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3703; 12913</t>
+          <t>3575; 12571</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28576; 45662</t>
+          <t>29682; 46344</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35724; 53427</t>
+          <t>35659; 53225</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29855; 44926</t>
+          <t>30246; 45841</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11757; 25355</t>
+          <t>11730; 24847</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40119; 59533</t>
+          <t>40742; 58503</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51214; 70204</t>
+          <t>50847; 69883</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43933; 63897</t>
+          <t>43537; 63780</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29068; 105071</t>
+          <t>29403; 113523</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32848; 49852</t>
+          <t>32642; 49540</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45702; 64942</t>
+          <t>45297; 65636</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>56040; 75564</t>
+          <t>54859; 76223</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31256; 52713</t>
+          <t>30693; 52227</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76024; 102113</t>
+          <t>77208; 101824</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>103061; 131021</t>
+          <t>103092; 130123</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>104204; 133108</t>
+          <t>104834; 134019</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>69640; 181059</t>
+          <t>67797; 157792</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16334; 28442</t>
+          <t>17049; 29962</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21109; 36795</t>
+          <t>20820; 36401</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26272; 41625</t>
+          <t>26155; 41677</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22072; 38117</t>
+          <t>22697; 38394</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>21832; 35450</t>
+          <t>22291; 36045</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25058; 41409</t>
+          <t>24998; 40204</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30696; 46774</t>
+          <t>30421; 45536</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18733; 36789</t>
+          <t>19310; 37159</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>42029; 61272</t>
+          <t>42541; 61199</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>50000; 71647</t>
+          <t>50672; 71308</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60922; 84316</t>
+          <t>61223; 84950</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>45444; 68972</t>
+          <t>44058; 70560</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16964; 30576</t>
+          <t>17812; 30300</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18963; 31041</t>
+          <t>18705; 31158</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17539; 29347</t>
+          <t>16940; 30199</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4493; 13728</t>
+          <t>4690; 14257</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14337; 26127</t>
+          <t>14569; 26817</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25969; 39450</t>
+          <t>25274; 39783</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20263; 33566</t>
+          <t>20046; 33680</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8325; 20112</t>
+          <t>8541; 20370</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>35237; 52672</t>
+          <t>34933; 52771</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48081; 66421</t>
+          <t>47528; 66363</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41368; 59603</t>
+          <t>40368; 58282</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15062; 30407</t>
+          <t>14649; 29425</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>124058; 157946</t>
+          <t>124621; 155811</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>165150; 199619</t>
+          <t>164635; 199800</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>165047; 198858</t>
+          <t>164518; 199461</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>113120; 223862</t>
+          <t>113470; 221006</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>130804; 162956</t>
+          <t>132896; 166042</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>187751; 224557</t>
+          <t>187232; 224232</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>195603; 232052</t>
+          <t>192946; 231250</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>108990; 148128</t>
+          <t>109849; 148481</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>264699; 312169</t>
+          <t>266221; 312573</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>363027; 412614</t>
+          <t>361476; 414824</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>367665; 421624</t>
+          <t>369547; 420621</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>235970; 354353</t>
+          <t>236316; 357352</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P5_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P5_R-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>26,21%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>43,34%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>39,11%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18,54%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>27,81%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>37,65%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>39,87%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19,3%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>26,21%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>43,34%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,11%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,25; 36,14</t>
+          <t>18,83; 35,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,89; 48,01</t>
+          <t>33,71; 53,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,33; 50,41</t>
+          <t>30,89; 48,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,67; 25,76</t>
+          <t>12,96; 25,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,87; 35,28</t>
+          <t>21,07; 36,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,28; 52,03</t>
+          <t>28,04; 47,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,95; 47,85</t>
+          <t>30,97; 49,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,98; 24,27</t>
+          <t>13,42; 26,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,35; 32,74</t>
+          <t>21,49; 33,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33,09; 47,73</t>
+          <t>34,28; 47,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,1; 45,82</t>
+          <t>32,69; 46,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,58; 23,22</t>
+          <t>14,91; 24,11</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20,17%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>45,14%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>33,74%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16,42%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>17,97%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>36,83%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>35,19%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17,85%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>20,17%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>45,14%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>33,74%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,06; 26,87</t>
+          <t>12,95; 28,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,58; 46,67</t>
+          <t>35,82; 55,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,95; 43,93</t>
+          <t>26,37; 41,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,91; 25,03</t>
+          <t>10,39; 24,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,17; 29,81</t>
+          <t>10,85; 25,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,95; 55,24</t>
+          <t>27,71; 46,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,44; 42,07</t>
+          <t>26,86; 44,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,64; 23,73</t>
+          <t>12,27; 25,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,2; 25,03</t>
+          <t>14,31; 24,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,9; 48,78</t>
+          <t>33,98; 48,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,15; 40,26</t>
+          <t>29,05; 40,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,26; 22,63</t>
+          <t>13,03; 23,21</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>30,18%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>34,68%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>34,29%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11,74%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>19,97%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>31,26%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>33,59%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19,85%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>30,18%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>34,68%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>34,29%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,33; 29,77</t>
+          <t>22,76; 38,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,01; 41,9</t>
+          <t>25,73; 45,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,77; 45,17</t>
+          <t>25,41; 44,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,39; 30,58</t>
+          <t>5,76; 21,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,44; 38,81</t>
+          <t>12,25; 29,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,56; 45,11</t>
+          <t>22,86; 41,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,39; 44,72</t>
+          <t>23,56; 44,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 19,69</t>
+          <t>11,06; 30,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,88; 32,59</t>
+          <t>20,43; 32,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,51; 39,58</t>
+          <t>26,74; 40,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27,44; 41,59</t>
+          <t>27,56; 41,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,14; 21,47</t>
+          <t>10,38; 22,07</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>27,56%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34,2%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>38,26%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18,88%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>32,21%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>44,25%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>32,22%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>25,45%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>27,56%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>34,2%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>38,26%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,93; 38,67</t>
+          <t>22,08; 34,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,26; 51,2</t>
+          <t>27,87; 40,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,26; 38,47</t>
+          <t>31,91; 44,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,52; 52,22</t>
+          <t>14,6; 24,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,97; 33,35</t>
+          <t>26,6; 38,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,07; 40,68</t>
+          <t>37,5; 51,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,1; 44,61</t>
+          <t>26,21; 38,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,06; 23,93</t>
+          <t>12,14; 23,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,75; 33,96</t>
+          <t>26,32; 34,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34,61; 43,69</t>
+          <t>34,6; 43,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31,14; 39,81</t>
+          <t>31,27; 39,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,56; 36,22</t>
+          <t>14,69; 21,57</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>34,03%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35,05%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>38,61%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16,98%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>32,41%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>30,53%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>33,63%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>25,1%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>34,03%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>35,05%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>38,61%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,66; 43,35</t>
+          <t>26,3; 42,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,28; 38,95</t>
+          <t>27,05; 43,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,75; 41,03</t>
+          <t>30,0; 47,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,0; 32,15</t>
+          <t>11,69; 22,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,37; 42,64</t>
+          <t>24,18; 41,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,17; 43,7</t>
+          <t>22,94; 39,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,68; 45,93</t>
+          <t>26,6; 41,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,87; 22,85</t>
+          <t>19,27; 32,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,69; 39,83</t>
+          <t>27,48; 39,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27,32; 38,45</t>
+          <t>27,5; 38,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,5; 42,32</t>
+          <t>31,07; 42,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,62; 25,02</t>
+          <t>16,79; 25,26</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>27,94%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>43,75%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>39,51%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>18,43%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>31,12%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>45,57%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>39,26%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12,2%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>27,94%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>43,75%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>39,51%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,79; 40,47</t>
+          <t>19,76; 36,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34,7; 57,79</t>
+          <t>35,42; 53,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,63; 51,04</t>
+          <t>29,28; 49,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,81; 20,69</t>
+          <t>10,47; 27,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,12; 37,04</t>
+          <t>23,3; 40,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,14; 53,73</t>
+          <t>34,74; 58,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,55; 49,66</t>
+          <t>29,2; 49,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,86; 28,29</t>
+          <t>6,01; 18,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,72; 35,83</t>
+          <t>23,66; 36,03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37,15; 51,87</t>
+          <t>37,96; 52,33</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31,79; 45,89</t>
+          <t>31,93; 46,09</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,4; 20,88</t>
+          <t>10,15; 20,68</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>27,93%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>38,37%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>37,42%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>17,45%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>28,0%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>38,03%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>34,83%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>21,48%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>38,37%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>37,42%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>24,79; 31,0</t>
+          <t>24,8; 31,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>34,52; 41,89</t>
+          <t>34,7; 41,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,46; 38,14</t>
+          <t>33,87; 40,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,28; 33,65</t>
+          <t>14,89; 20,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,14; 31,41</t>
+          <t>25,0; 31,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,85; 41,73</t>
+          <t>34,46; 41,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,84; 40,56</t>
+          <t>31,59; 38,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,68; 19,84</t>
+          <t>16,22; 21,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,82; 30,31</t>
+          <t>25,63; 30,1</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35,64; 40,9</t>
+          <t>35,82; 40,73</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33,81; 38,48</t>
+          <t>34,04; 38,97</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,82; 25,43</t>
+          <t>16,28; 20,08</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18774</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>31813</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>30605</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22547</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>22371</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>23050</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>25846</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>20163</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>18774</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31813</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>30605</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24052</t>
+          <t>20048</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44216</t>
+          <t>42595</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16291; 29078</t>
+          <t>13487; 25638</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17074; 29395</t>
+          <t>24745; 39033</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19661; 32679</t>
+          <t>24169; 37727</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14283; 26908</t>
+          <t>15760; 30754</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13520; 25274</t>
+          <t>16948; 29682</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24430; 38194</t>
+          <t>17166; 29190</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23435; 37444</t>
+          <t>20078; 32269</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16284; 32994</t>
+          <t>13815; 27579</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32470; 49795</t>
+          <t>32683; 50200</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44552; 64263</t>
+          <t>46145; 64537</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45928; 65567</t>
+          <t>46780; 66818</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35065; 55816</t>
+          <t>33479; 54145</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13614</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30933</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>31400</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>15004</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>12343</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>24076</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>28965</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16904</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13614</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>30933</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>31400</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15769</t>
+          <t>17109</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32673</t>
+          <t>32113</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7594; 18454</t>
+          <t>8739; 19245</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17375; 30515</t>
+          <t>24549; 37962</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22183; 36161</t>
+          <t>24542; 39031</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11275; 23699</t>
+          <t>9492; 22243</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8888; 20117</t>
+          <t>7454; 17805</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24636; 37851</t>
+          <t>18115; 30535</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24608; 39152</t>
+          <t>22111; 36512</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10171; 22680</t>
+          <t>11849; 24342</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19341; 34087</t>
+          <t>19489; 33662</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45391; 65313</t>
+          <t>45506; 64444</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51114; 70599</t>
+          <t>50956; 70921</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25222; 43052</t>
+          <t>24489; 43620</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>25332</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23568</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>20918</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6685</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>11630</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>20794</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>16534</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10295</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>25332</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>23568</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>20918</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>10369</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17398</t>
+          <t>17054</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7182; 17342</t>
+          <t>19106; 32132</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15308; 27873</t>
+          <t>17488; 30667</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11700; 22235</t>
+          <t>15502; 27435</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5906; 15861</t>
+          <t>3280; 12036</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18837; 32581</t>
+          <t>7133; 17149</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17374; 30658</t>
+          <t>15208; 27338</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15489; 27284</t>
+          <t>11599; 22084</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3575; 12571</t>
+          <t>5917; 16152</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29682; 46344</t>
+          <t>29047; 45825</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35659; 53225</t>
+          <t>35963; 54028</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30246; 45841</t>
+          <t>30379; 46110</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11730; 24847</t>
+          <t>11462; 24368</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>41</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>40937</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>55188</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>65388</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38123</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>48727</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>60391</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>53412</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>55323</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>40937</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>55188</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>65388</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41089</t>
+          <t>29459</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96412</t>
+          <t>67582</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40742; 58503</t>
+          <t>32807; 50718</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50847; 69883</t>
+          <t>44975; 65860</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43537; 63780</t>
+          <t>54529; 75349</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29403; 113523</t>
+          <t>29484; 50476</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32642; 49540</t>
+          <t>40238; 58456</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45297; 65636</t>
+          <t>51182; 70292</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54859; 76223</t>
+          <t>43451; 63264</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30693; 52227</t>
+          <t>21752; 41557</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>77208; 101824</t>
+          <t>78928; 102941</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>103092; 130123</t>
+          <t>103043; 130842</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>104834; 134019</t>
+          <t>105275; 134330</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>67797; 157792</t>
+          <t>55976; 82195</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>46</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>28762</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>32247</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>38282</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>25168</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>22402</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>28531</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>34163</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>29979</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>28762</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>32247</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38282</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27339</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>57318</t>
+          <t>55940</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17049; 29962</t>
+          <t>22235; 35622</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20820; 36401</t>
+          <t>24885; 39691</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26155; 41677</t>
+          <t>29747; 46647</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22697; 38394</t>
+          <t>17327; 34084</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>22291; 36045</t>
+          <t>16713; 28795</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24998; 40204</t>
+          <t>21439; 36813</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30421; 45536</t>
+          <t>27022; 41750</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19310; 37159</t>
+          <t>22877; 38722</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>42541; 61199</t>
+          <t>42231; 60679</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>50672; 71308</t>
+          <t>50993; 71825</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>61223; 84950</t>
+          <t>62365; 84539</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>44058; 70560</t>
+          <t>44831; 67449</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>20229</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>32392</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>26801</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>12584</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>23300</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>24566</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>23228</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>8405</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>20229</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>32392</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>26801</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>7874</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>20459</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17812; 30300</t>
+          <t>14306; 26654</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18705; 31158</t>
+          <t>26224; 39689</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16940; 30199</t>
+          <t>19857; 33624</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4690; 14257</t>
+          <t>7151; 18669</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14569; 26817</t>
+          <t>17446; 30089</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25274; 39783</t>
+          <t>18731; 31342</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20046; 33680</t>
+          <t>17279; 29495</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8541; 20370</t>
+          <t>4226; 13162</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>34933; 52771</t>
+          <t>34846; 53057</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>47528; 66363</t>
+          <t>48571; 66959</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40368; 58282</t>
+          <t>40542; 58535</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14649; 29425</t>
+          <t>14079; 28672</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>256</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>275</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>168</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>147647</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>206142</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>213394</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>120111</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>140772</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>181408</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>182148</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>141070</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>147647</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>206142</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>213394</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>128662</t>
+          <t>115631</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>269732</t>
+          <t>235742</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>124621; 155811</t>
+          <t>131055; 164091</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>164635; 199800</t>
+          <t>186434; 224936</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>164518; 199461</t>
+          <t>193152; 231741</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>113470; 221006</t>
+          <t>102504; 139989</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>132896; 166042</t>
+          <t>125664; 157404</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>187232; 224232</t>
+          <t>164366; 199035</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>192946; 231250</t>
+          <t>165189; 200681</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>109849; 148481</t>
+          <t>100783; 133739</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>266221; 312573</t>
+          <t>264328; 310372</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>361476; 414824</t>
+          <t>363335; 413120</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>369547; 420621</t>
+          <t>372060; 425961</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>236316; 357352</t>
+          <t>213177; 262984</t>
         </is>
       </c>
     </row>
